--- a/target/target.xlsx
+++ b/target/target.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryanzhang/Desktop/sunchha_community_agent/target/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryanzhang/Desktop/github/sunchha_community_agent-main/target/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEE14F68-4D81-714B-8B49-329185586583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84E63AF6-4873-6346-AE7F-C2307EC48818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17820" xr2:uid="{992D1E47-7490-1A46-80E1-AB49E24758D4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>num</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -91,6 +91,18 @@
   </si>
   <si>
     <t>192.168.2.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commands</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>display version,display vlan,display memory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>show vlan,show interface,show memory</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -149,12 +161,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -491,13 +506,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF5590D-908D-514A-9773-C649A992112B}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="6" max="6" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="32.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -519,8 +535,11 @@
       <c r="G1" t="s">
         <v>7</v>
       </c>
+      <c r="H1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8" ht="34">
       <c r="A2">
         <v>1</v>
       </c>
@@ -542,8 +561,11 @@
       <c r="G2" t="s">
         <v>10</v>
       </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8" ht="34">
       <c r="A3">
         <v>2</v>
       </c>
@@ -564,6 +586,9 @@
       </c>
       <c r="G3" t="s">
         <v>11</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
